--- a/reports/latest/Excel/Failed_Test_Cases.xlsx
+++ b/reports/latest/Excel/Failed_Test_Cases.xlsx
@@ -11,92 +11,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Test ID</t>
   </si>
   <si>
+    <t>Suite / Platform</t>
+  </si>
+  <si>
     <t>Module</t>
   </si>
   <si>
     <t>Test Name</t>
   </si>
   <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Execution Time (ms)</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Preconditions</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
+    <t>Duration (ms)</t>
   </si>
   <si>
     <t>Failure Reason</t>
-  </si>
-  <si>
-    <t>SEL-AUTH-001</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Authentication Automated Scenario 1</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>P0</t>
-  </si>
-  <si>
-    <t>User is logged out and on the Login screen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Input email address variation 1
-2. Enter corresponding password credentials
-3. Click "Submit" button</t>
-  </si>
-  <si>
-    <t>User session is authenticated and user is redirected to the home dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutError: Waiting for element to be located By(css selector, input[placeholder*="Email"], [data-testid="email-input"] input, input[type="email"])
-Wait timed out after 15137ms
-    at /home/runner/work/PantryMobileApp/PantryMobileApp/automation/node_modules/selenium-webdriver/lib/webdriver.js:929:22
-    at process.processTicksAndRejections (node:internal/process/task_queues:95:5)</t>
-  </si>
-  <si>
-    <t>SEL-AUTH-002</t>
-  </si>
-  <si>
-    <t>Authentication Automated Scenario 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Input email address variation 2
-2. Enter corresponding password credentials
-3. Click "Submit" button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutError: Waiting for element to be located By(css selector, input[placeholder*="Email"], [data-testid="email-input"] input, input[type="email"])
-Wait timed out after 15161ms
-    at /home/runner/work/PantryMobileApp/PantryMobileApp/automation/node_modules/selenium-webdriver/lib/webdriver.js:929:22
-    at process.processTicksAndRejections (node:internal/process/task_queues:95:5)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -108,20 +53,10 @@
       <b/>
       <color rgb="FFFFFF"/>
       <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="991B1B"/>
-      <sz val="9"/>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,16 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0F172A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,25 +96,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,21 +440,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="9" width="45" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,76 +477,6 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2">
-        <v>21295</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5">
-        <v>20462</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
